--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117960342</v>
+        <v>117960429</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592404</v>
+        <v>592412</v>
       </c>
       <c r="R2" t="n">
-        <v>6983776</v>
+        <v>6983818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117960112</v>
+        <v>117960342</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592378</v>
+        <v>592404</v>
       </c>
       <c r="R3" t="n">
-        <v>6983734</v>
+        <v>6983776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117960036</v>
+        <v>117960568</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,31 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592373</v>
+        <v>592383</v>
       </c>
       <c r="R4" t="n">
-        <v>6983743</v>
+        <v>6983824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,19 +1007,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117960359</v>
+        <v>117960481</v>
       </c>
       <c r="B5" t="n">
         <v>79561</v>
@@ -1061,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592401</v>
+        <v>592368</v>
       </c>
       <c r="R5" t="n">
-        <v>6983755</v>
+        <v>6983850</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117960085</v>
+        <v>117960112</v>
       </c>
       <c r="B6" t="n">
-        <v>97756</v>
+        <v>57287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,31 +1143,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592390</v>
+        <v>592378</v>
       </c>
       <c r="R6" t="n">
-        <v>6983747</v>
+        <v>6983734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117960481</v>
+        <v>117960448</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,38 +1260,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592368</v>
+        <v>592389</v>
       </c>
       <c r="R7" t="n">
-        <v>6983850</v>
+        <v>6983833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117960448</v>
+        <v>117960359</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,45 +1376,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592389</v>
+        <v>592401</v>
       </c>
       <c r="R8" t="n">
-        <v>6983833</v>
+        <v>6983755</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,7 +1476,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117960568</v>
+        <v>117960553</v>
       </c>
       <c r="B9" t="n">
         <v>97836</v>
@@ -1513,7 +1511,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592383</v>
+        <v>592404</v>
       </c>
       <c r="R9" t="n">
-        <v>6983824</v>
+        <v>6983816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,19 +1580,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117960477</v>
+        <v>117960421</v>
       </c>
       <c r="B10" t="n">
         <v>79561</v>
@@ -1634,7 +1632,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592424</v>
+        <v>592384</v>
       </c>
       <c r="R10" t="n">
         <v>6983814</v>
@@ -1669,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,19 +1692,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117960421</v>
+        <v>117960477</v>
       </c>
       <c r="B11" t="n">
         <v>79561</v>
@@ -1746,7 +1744,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592384</v>
+        <v>592424</v>
       </c>
       <c r="R11" t="n">
         <v>6983814</v>
@@ -1781,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,22 +1804,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117960553</v>
+        <v>117960085</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97756</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,30 +1828,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1862,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592404</v>
+        <v>592390</v>
       </c>
       <c r="R12" t="n">
-        <v>6983816</v>
+        <v>6983747</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,22 +1921,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117960429</v>
+        <v>117960036</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,30 +1945,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592412</v>
+        <v>592373</v>
       </c>
       <c r="R13" t="n">
-        <v>6983818</v>
+        <v>6983743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117960429</v>
+        <v>117960421</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592412</v>
+        <v>592384</v>
       </c>
       <c r="R2" t="n">
-        <v>6983818</v>
+        <v>6983814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117960342</v>
+        <v>117960477</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592404</v>
+        <v>592424</v>
       </c>
       <c r="R3" t="n">
-        <v>6983776</v>
+        <v>6983814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117960568</v>
+        <v>117960481</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592383</v>
+        <v>592368</v>
       </c>
       <c r="R4" t="n">
-        <v>6983824</v>
+        <v>6983850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117960481</v>
+        <v>117960553</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,38 +1023,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592368</v>
+        <v>592404</v>
       </c>
       <c r="R5" t="n">
-        <v>6983850</v>
+        <v>6983816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117960112</v>
+        <v>117960342</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,39 +1143,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592378</v>
+        <v>592404</v>
       </c>
       <c r="R6" t="n">
-        <v>6983734</v>
+        <v>6983776</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117960448</v>
+        <v>117960568</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,7 +1274,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592389</v>
+        <v>592383</v>
       </c>
       <c r="R7" t="n">
-        <v>6983833</v>
+        <v>6983824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1358,7 @@
         <v>117960359</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117960553</v>
+        <v>117960429</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,7 +1502,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1520,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592404</v>
+        <v>592412</v>
       </c>
       <c r="R9" t="n">
-        <v>6983816</v>
+        <v>6983818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117960421</v>
+        <v>117960448</v>
       </c>
       <c r="B10" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,38 +1595,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592384</v>
+        <v>592389</v>
       </c>
       <c r="R10" t="n">
-        <v>6983814</v>
+        <v>6983833</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1672,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117960477</v>
+        <v>117960036</v>
       </c>
       <c r="B11" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,34 +1715,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gullabborrtjärnmyran (Gullabborrtjärnmyran), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592424</v>
+        <v>592373</v>
       </c>
       <c r="R11" t="n">
-        <v>6983814</v>
+        <v>6983743</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,7 +1819,7 @@
         <v>117960085</v>
       </c>
       <c r="B12" t="n">
-        <v>97756</v>
+        <v>97758</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117960036</v>
+        <v>117960112</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592373</v>
+        <v>592378</v>
       </c>
       <c r="R13" t="n">
-        <v>6983743</v>
+        <v>6983734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117960429</v>
+        <v>117960085</v>
       </c>
       <c r="B9" t="n">
-        <v>97838</v>
+        <v>97758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,30 +1479,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592412</v>
+        <v>592390</v>
       </c>
       <c r="R9" t="n">
-        <v>6983818</v>
+        <v>6983747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,22 +1572,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117960448</v>
+        <v>117960036</v>
       </c>
       <c r="B10" t="n">
-        <v>97838</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,30 +1596,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1627,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592389</v>
+        <v>592373</v>
       </c>
       <c r="R10" t="n">
-        <v>6983833</v>
+        <v>6983743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,22 +1689,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117960036</v>
+        <v>117960429</v>
       </c>
       <c r="B11" t="n">
-        <v>57288</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,31 +1713,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1744,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592373</v>
+        <v>592412</v>
       </c>
       <c r="R11" t="n">
-        <v>6983743</v>
+        <v>6983818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117960085</v>
+        <v>117960448</v>
       </c>
       <c r="B12" t="n">
-        <v>97758</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,31 +1829,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592390</v>
+        <v>592389</v>
       </c>
       <c r="R12" t="n">
-        <v>6983747</v>
+        <v>6983833</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117960112</v>
+        <v>117960036</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1852,7 +1852,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592378</v>
+        <v>592373</v>
       </c>
       <c r="R12" t="n">
-        <v>6983734</v>
+        <v>6983743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117960036</v>
+        <v>117960112</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1969,7 +1969,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592373</v>
+        <v>592378</v>
       </c>
       <c r="R13" t="n">
-        <v>6983743</v>
+        <v>6983734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117960036</v>
+        <v>117960112</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1852,7 +1852,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592373</v>
+        <v>592378</v>
       </c>
       <c r="R12" t="n">
-        <v>6983743</v>
+        <v>6983734</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117960112</v>
+        <v>117960036</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1969,7 +1969,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592378</v>
+        <v>592373</v>
       </c>
       <c r="R13" t="n">
-        <v>6983734</v>
+        <v>6983743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -2053,11 +2053,11 @@
         <v>117960028</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>117960028</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10214-2024 artfynd.xlsx
+++ b/artfynd/A 10214-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>117960028</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
